--- a/assets_output/05_univariate_characteristics.xlsx
+++ b/assets_output/05_univariate_characteristics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="89">
   <si>
     <t>Frequencies for gender</t>
   </si>
@@ -50,6 +50,66 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Frequencies for ethnicity_grouped</t>
+  </si>
+  <si>
+    <t>ethnicity_grouped</t>
+  </si>
+  <si>
+    <t>Arab</t>
+  </si>
+  <si>
+    <t>Asian/Asian British</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Mixed Heritage</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Frequencies for ethnicity_detailed</t>
+  </si>
+  <si>
+    <t>ethnicity_detailed</t>
+  </si>
+  <si>
+    <t>Any other Mixed/multiple ethnic background</t>
+  </si>
+  <si>
+    <t>Black/Black British - African</t>
+  </si>
+  <si>
+    <t>Black/Black British - Caribbean</t>
+  </si>
+  <si>
+    <t>Black/Black British - Other</t>
+  </si>
+  <si>
+    <t>Mixed/Dual Heritage - White+Black African</t>
+  </si>
+  <si>
+    <t>Mixed/Dual Heritage - White+Black Caribbean</t>
+  </si>
+  <si>
+    <t>White British</t>
+  </si>
+  <si>
+    <t>White Gypsy/Irish Traveller</t>
+  </si>
+  <si>
+    <t>White Other</t>
   </si>
   <si>
     <t>Frequencies for age_cat</t>
@@ -578,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -723,10 +783,10 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -734,10 +794,10 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="C19">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -745,10 +805,10 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <v>1181</v>
+        <v>497</v>
       </c>
       <c r="C20">
-        <v>31.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -756,10 +816,10 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <v>1166</v>
+        <v>196</v>
       </c>
       <c r="C21">
-        <v>31.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -767,10 +827,10 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>759</v>
+        <v>53</v>
       </c>
       <c r="C22">
-        <v>20.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -778,10 +838,10 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="C23">
-        <v>6.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -789,598 +849,659 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>48</v>
+        <v>2658</v>
       </c>
       <c r="C24">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1"/>
+      <c r="B25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28">
-        <v>2673</v>
-      </c>
-      <c r="C28">
-        <v>71.2</v>
+        <v>22</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>879</v>
+        <v>46</v>
       </c>
       <c r="C29">
-        <v>23.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B30">
-        <v>202</v>
+        <v>57</v>
       </c>
       <c r="C30">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="B31">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="C31">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32">
+        <v>280</v>
+      </c>
+      <c r="C32">
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>23</v>
+      <c r="A33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33">
+        <v>145</v>
+      </c>
+      <c r="C33">
+        <v>3.9</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="B34">
+        <v>72</v>
+      </c>
+      <c r="C34">
+        <v>1.9</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="1" t="b">
-        <v>0</v>
+      <c r="A35" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B35">
-        <v>2568</v>
+        <v>35</v>
       </c>
       <c r="C35">
-        <v>83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="1" t="b">
-        <v>1</v>
+      <c r="A36" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B36">
-        <v>526</v>
+        <v>115</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="B37">
-        <v>661</v>
+        <v>53</v>
+      </c>
+      <c r="C37">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38">
+        <v>188</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>25</v>
+      <c r="A39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39">
+        <v>2447</v>
+      </c>
+      <c r="C39">
+        <v>65.2</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="B40">
+        <v>13</v>
+      </c>
+      <c r="C40">
+        <v>0.3</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1" t="b">
-        <v>0</v>
+      <c r="A41" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B41">
-        <v>1956</v>
+        <v>198</v>
       </c>
       <c r="C41">
-        <v>63.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="1" t="b">
-        <v>1</v>
-      </c>
+      <c r="A42" s="1"/>
       <c r="B42">
-        <v>1138</v>
-      </c>
-      <c r="C42">
-        <v>36.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1"/>
-      <c r="B43">
-        <v>661</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>27</v>
+      <c r="A45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="1" t="b">
-        <v>1</v>
+      <c r="A47" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B47">
-        <v>2181</v>
+        <v>340</v>
       </c>
       <c r="C47">
-        <v>70.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="1" t="b">
-        <v>0</v>
+      <c r="A48" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="B48">
-        <v>913</v>
+        <v>1181</v>
       </c>
       <c r="C48">
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="1"/>
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="B49">
-        <v>661</v>
+        <v>1166</v>
+      </c>
+      <c r="C49">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50">
+        <v>759</v>
+      </c>
+      <c r="C50">
+        <v>20.2</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>29</v>
+      <c r="A51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51">
+        <v>260</v>
+      </c>
+      <c r="C51">
+        <v>6.9</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B53">
-        <v>1489</v>
-      </c>
-      <c r="C53">
-        <v>48.1</v>
+        <v>40</v>
+      </c>
+      <c r="B52">
+        <v>48</v>
+      </c>
+      <c r="C52">
+        <v>1.3</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B54">
-        <v>1605</v>
-      </c>
-      <c r="C54">
-        <v>51.9</v>
+      <c r="A54" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="1"/>
-      <c r="B55">
-        <v>661</v>
+      <c r="A55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>2673</v>
+      </c>
+      <c r="C56">
+        <v>71.2</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>31</v>
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57">
+        <v>879</v>
+      </c>
+      <c r="C57">
+        <v>23.4</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="B58">
+        <v>202</v>
+      </c>
+      <c r="C58">
+        <v>5.4</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="1" t="b">
+      <c r="A59" s="1"/>
+      <c r="B59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B59">
-        <v>1458</v>
-      </c>
-      <c r="C59">
-        <v>47.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B60">
-        <v>1636</v>
-      </c>
-      <c r="C60">
-        <v>52.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1"/>
-      <c r="B61">
+      <c r="B63">
+        <v>2568</v>
+      </c>
+      <c r="C63">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B64">
+        <v>526</v>
+      </c>
+      <c r="C64">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1"/>
+      <c r="B65">
         <v>661</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1" t="b">
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B65">
-        <v>2452</v>
-      </c>
-      <c r="C65">
-        <v>79.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B66">
-        <v>642</v>
-      </c>
-      <c r="C66">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1"/>
-      <c r="B67">
+      <c r="B69">
+        <v>1956</v>
+      </c>
+      <c r="C69">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B70">
+        <v>1138</v>
+      </c>
+      <c r="C70">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1"/>
+      <c r="B71">
         <v>661</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="1" t="b">
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B75">
+        <v>2181</v>
+      </c>
+      <c r="C75">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B71">
-        <v>3038</v>
-      </c>
-      <c r="C71">
-        <v>98.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="1"/>
-      <c r="B72">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B73">
-        <v>56</v>
-      </c>
-      <c r="C73">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>2</v>
+      <c r="B76">
+        <v>913</v>
+      </c>
+      <c r="C76">
+        <v>29.5</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1"/>
       <c r="B77">
-        <v>2921</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="1" t="b">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B78">
-        <v>780</v>
-      </c>
-      <c r="C78">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B79">
-        <v>54</v>
-      </c>
-      <c r="C79">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>39</v>
+      <c r="B81">
+        <v>1489</v>
+      </c>
+      <c r="C81">
+        <v>48.1</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>2</v>
+      <c r="A82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B82">
+        <v>1605</v>
+      </c>
+      <c r="C82">
+        <v>51.9</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="1" t="b">
+      <c r="A83" s="1"/>
+      <c r="B83">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B83">
-        <v>2181</v>
-      </c>
-      <c r="C83">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="1"/>
-      <c r="B84">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>2</v>
+      <c r="B87">
+        <v>1458</v>
+      </c>
+      <c r="C87">
+        <v>47.1</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B88">
+        <v>1636</v>
+      </c>
+      <c r="C88">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="1"/>
+      <c r="B89">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B88">
-        <v>2546</v>
-      </c>
-      <c r="C88">
-        <v>82.3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B89">
-        <v>548</v>
-      </c>
-      <c r="C89">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="1"/>
-      <c r="B90">
+      <c r="B93">
+        <v>2452</v>
+      </c>
+      <c r="C93">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B94">
+        <v>642</v>
+      </c>
+      <c r="C94">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1"/>
+      <c r="B95">
         <v>661</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="1"/>
-      <c r="B94">
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B99">
+        <v>3038</v>
+      </c>
+      <c r="C99">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1"/>
+      <c r="B100">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B101">
+        <v>56</v>
+      </c>
+      <c r="C101">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1"/>
+      <c r="B105">
         <v>2921</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B95">
-        <v>508</v>
-      </c>
-      <c r="C95">
-        <v>60.9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B96">
-        <v>326</v>
-      </c>
-      <c r="C96">
-        <v>39.1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B100">
-        <v>1978</v>
-      </c>
-      <c r="C100">
-        <v>90.7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="1"/>
-      <c r="B101">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B102">
-        <v>203</v>
-      </c>
-      <c r="C102">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1388,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="B106">
-        <v>2846</v>
+        <v>780</v>
       </c>
       <c r="C106">
-        <v>92</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1399,289 +1520,492 @@
         <v>1</v>
       </c>
       <c r="B107">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="C107">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="1"/>
-      <c r="B108">
-        <v>661</v>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" t="s">
-        <v>49</v>
+      <c r="A110" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>2</v>
+      <c r="A111" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B111">
+        <v>2181</v>
+      </c>
+      <c r="C111">
+        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="1"/>
       <c r="B112">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B116">
+        <v>2546</v>
+      </c>
+      <c r="C116">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B117">
+        <v>548</v>
+      </c>
+      <c r="C117">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1"/>
+      <c r="B118">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="1"/>
+      <c r="B122">
         <v>2921</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="1" t="b">
+    <row r="123" spans="1:3">
+      <c r="A123" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B113">
-        <v>720</v>
-      </c>
-      <c r="C113">
-        <v>86.3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B114">
-        <v>114</v>
-      </c>
-      <c r="C114">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B118">
-        <v>2052</v>
-      </c>
-      <c r="C118">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B119">
-        <v>129</v>
-      </c>
-      <c r="C119">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="1"/>
-      <c r="B120">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>2</v>
+      <c r="B123">
+        <v>508</v>
+      </c>
+      <c r="C123">
+        <v>60.9</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
-        <v>55</v>
+      <c r="A124" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="B124">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C124">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B125">
-        <v>2723</v>
-      </c>
-      <c r="C125">
-        <v>86.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="1"/>
-      <c r="B126">
-        <v>601</v>
+      <c r="A126" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B127">
-        <v>109</v>
-      </c>
-      <c r="C127">
-        <v>3.5</v>
+        <v>66</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B128">
+        <v>1978</v>
+      </c>
+      <c r="C128">
+        <v>90.7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" t="s">
-        <v>58</v>
+      <c r="A129" s="1"/>
+      <c r="B129">
+        <v>1574</v>
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B131">
-        <v>3354</v>
-      </c>
-      <c r="C131">
-        <v>89.3</v>
+      <c r="A130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B130">
+        <v>203</v>
+      </c>
+      <c r="C130">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B132">
-        <v>401</v>
-      </c>
-      <c r="C132">
-        <v>10.7</v>
+      <c r="A132" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" t="s">
-        <v>60</v>
+      <c r="A134" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B134">
+        <v>2846</v>
+      </c>
+      <c r="C134">
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>2</v>
+      <c r="A135" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B135">
+        <v>248</v>
+      </c>
+      <c r="C135">
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="A136" s="1"/>
       <c r="B136">
-        <v>1600</v>
-      </c>
-      <c r="C136">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B137">
-        <v>226</v>
-      </c>
-      <c r="C137">
-        <v>6</v>
+        <v>661</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B138">
-        <v>618</v>
-      </c>
-      <c r="C138">
-        <v>16.5</v>
+      <c r="A138" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B139">
+        <v>70</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="1"/>
+      <c r="B140">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B141">
+        <v>720</v>
+      </c>
+      <c r="C141">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B142">
+        <v>114</v>
+      </c>
+      <c r="C142">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B146">
+        <v>2052</v>
+      </c>
+      <c r="C146">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B147">
+        <v>129</v>
+      </c>
+      <c r="C147">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="1"/>
+      <c r="B148">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B152">
+        <v>322</v>
+      </c>
+      <c r="C152">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B153">
+        <v>2723</v>
+      </c>
+      <c r="C153">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="1"/>
+      <c r="B154">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B155">
+        <v>109</v>
+      </c>
+      <c r="C155">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159">
+        <v>3354</v>
+      </c>
+      <c r="C159">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160">
+        <v>401</v>
+      </c>
+      <c r="C160">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B164">
+        <v>1600</v>
+      </c>
+      <c r="C164">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B165">
+        <v>226</v>
+      </c>
+      <c r="C165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B166">
+        <v>618</v>
+      </c>
+      <c r="C166">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B167">
         <v>289</v>
       </c>
-      <c r="C139">
+      <c r="C167">
         <v>7.7</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B140">
+    <row r="168" spans="1:3">
+      <c r="A168" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B168">
         <v>763</v>
       </c>
-      <c r="C140">
+      <c r="C168">
         <v>20.3</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B141">
+    <row r="169" spans="1:3">
+      <c r="A169" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B169">
         <v>111</v>
       </c>
-      <c r="C141">
+      <c r="C169">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B142">
+    <row r="170" spans="1:3">
+      <c r="A170" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B170">
         <v>148</v>
       </c>
-      <c r="C142">
+      <c r="C170">
         <v>3.9</v>
       </c>
     </row>
